--- a/装配BOM-机械行者Robo-2026-10-23-带采购链接.xlsx
+++ b/装配BOM-机械行者Robo-2026-10-23-带采购链接.xlsx
@@ -3448,7 +3448,7 @@
     <hyperlink ref="J37" r:id="rId2" display="https://item.taobao.com/item.htm?id=763812025816&amp;last_time=1790655696&amp;mi_id=0000M9KvAKZdKHX6irXd93nZ9S8044VLMp9XHfosSxlXgV0&amp;scm=1007.13982.82927.0&amp;spm=tbpc.mytb_footmark.item.goods&amp;upStreamPrice=88800"/>
     <hyperlink ref="J48" r:id="rId3" display="https://item.taobao.com/item.htm?from=cart&amp;id=737603917521&amp;mi_id=0000svFiYCCRNyTplS2syupd6wPqm_3g253yiYEiJIUzYWg&amp;skuId=5090650052053&amp;spm=a1z0d.6639537%2F202410.item.d737603917521.12a97484LeTNU7&amp;upStreamPrice=4950" tooltip="https://item.taobao.com/item.htm?from=cart&amp;id=737603917521&amp;mi_id=0000svFiYCCRNyTplS2syupd6wPqm_3g253yiYEiJIUzYWg&amp;skuId=5090650052053&amp;spm=a1z0d.6639537%2F202410.item.d737603917521.12a97484LeTNU7&amp;upStreamPrice=4950"/>
     <hyperlink ref="J47" r:id="rId4" display="https://detail.tmall.com/item.htm?id=775872575316" tooltip="https://detail.tmall.com/item.htm?id=775872575316"/>
-    <hyperlink ref="J49" r:id="rId5" display="https://item.taobao.com/item.htm?ali_refid=a3_430673_1006%3A1300920180%3AH%3AXe0d%2B%2ByvvuheeXXsNbtAzA%3D%3D%3A1fb351596f290624d1f838f6933a4bf9&amp;ali_trackid=318_1fb351596f290624d1f838f6933a4bf9&amp;id=902489608878&amp;loginBonus=1&amp;mi_id=00004qd77Ss-NI_QwEGJk3oQMSCKLeGBjvYFB1womY2KPUQ&amp;mm_sceneid=0_0_1169600180_0_0&amp;priceTId=2100c91217905892639744554e0a2f&amp;skuId=5925223242747&amp;spm=a21n57.sem.item.52&amp;utparam=%7B%22aplus_abtest%22%3A%221116d3394ed69d4d6ae8676cf27ec828%22%7D&amp;xxc=ad_ztc"/>
+    <hyperlink ref="J49" r:id="rId5" display="https://item.taobao.com/item.htm?ali_refid=a3_430673_1006%3A1300920180%3AH%3AXe0d%2B%2ByvvuheeXXsNbtAzA%3D%3D%3A1fb351596f290624d1f838f6933a4bf9&amp;ali_trackid=318_1fb351596f290624d1f838f6933a4bf9&amp;id=902489608878&amp;loginBonus=1&amp;mi_id=00004qd77Ss-NI_QwEGJk3oQMSCKLeGBjvYFB1womY2KPUQ&amp;mm_sceneid=0_0_1169600180_0_0&amp;priceTId=2100c91217905892639744554e0a2f&amp;skuId=5925223242747&amp;spm=a21n57.sem.item.52&amp;utparam=%7B%22aplus_abtest%22%3A%221116d3394ed69d4d6ae8676cf27ec828%22%7D&amp;xxc=ad_ztc" tooltip="https://item.taobao.com/item.htm?ali_refid=a3_430673_1006%3A1300920180%3AH%3AXe0d%2B%2ByvvuheeXXsNbtAzA%3D%3D%3A1fb351596f290624d1f838f6933a4bf9&amp;ali_trackid=318_1fb351596f290624d1f838f6933a4bf9&amp;id=902489608878&amp;loginBonus=1&amp;mi_id=00004qd77Ss-NI_QwEGJk3oQMS"/>
     <hyperlink ref="J51" r:id="rId6" display="https://item.taobao.com/item.htm?id=539024647147&amp;skuId=5716548727712" tooltip="https://item.taobao.com/item.htm?id=539024647147&amp;skuId=5716548727712"/>
     <hyperlink ref="J50" r:id="rId7" display="https://item.taobao.com/item.htm?id=670727787832" tooltip="https://item.taobao.com/item.htm?id=670727787832"/>
     <hyperlink ref="J3" r:id="rId8" display="https://item.taobao.com/item.htm?from=cart&amp;id=1083122166800&amp;mi_id=0000ywbZ5efl4VxxIGb0KHx-3C8BOS37n90MGBh_xmncHd4&amp;skuId=6306393642451&amp;spm=a1z0d.6639537%2F202410.item.d1083122166800.70527484LqKlHG&amp;upStreamPrice=13900"/>
